--- a/example/en/import/04_edge_cases.xlsx
+++ b/example/en/import/04_edge_cases.xlsx
@@ -1,14 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edge" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CustomHeaderFooter" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Edge" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CustomHeaderFooter" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EarlyStop" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NoFirstRow" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -743,17 +745,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -932,4 +934,325 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Export type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>File header</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>return {</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Export file</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cfg_example_early_stop.lua</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>File footer</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>key count</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Above the blank row: exported</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sc</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>above_blank</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Above the blank row: exported too</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>above_text</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>kept</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Below the blank row: not exported</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>below_blank</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Below the blank row: not exported either</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>below_text</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>never written</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Export type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>File header</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>return {</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Export file</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cfg_example_no_first_row.lua</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>File footer</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>key count</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Row 6 is blank, so the table is not exported</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>never_read</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>